--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/139.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/139.xlsx
@@ -426,13 +426,13 @@
         <v>-11.94650000218507</v>
       </c>
       <c r="E2">
-        <v>-6.648811769671397</v>
+        <v>-7.576338344396447</v>
       </c>
       <c r="F2">
-        <v>-4.56019334925269</v>
+        <v>-5.193681521971792</v>
       </c>
       <c r="G2">
-        <v>-10.82323289366457</v>
+        <v>-11.37996431809867</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.09828903238887</v>
       </c>
       <c r="E3">
-        <v>-6.757123810986857</v>
+        <v>-7.710277020121314</v>
       </c>
       <c r="F3">
-        <v>-4.797704507718169</v>
+        <v>-5.006452264856242</v>
       </c>
       <c r="G3">
-        <v>-12.26648475902945</v>
+        <v>-12.461281039349</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.24546888626801</v>
       </c>
       <c r="E4">
-        <v>-7.45777836640163</v>
+        <v>-8.414214719191648</v>
       </c>
       <c r="F4">
-        <v>-4.535314162677009</v>
+        <v>-4.912877397933801</v>
       </c>
       <c r="G4">
-        <v>-12.17344572171139</v>
+        <v>-12.95150866521628</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.34175740762799</v>
       </c>
       <c r="E5">
-        <v>-7.941428447368839</v>
+        <v>-9.435036915422723</v>
       </c>
       <c r="F5">
-        <v>-4.38074329041683</v>
+        <v>-4.724152937656199</v>
       </c>
       <c r="G5">
-        <v>-12.34922076065085</v>
+        <v>-12.48802627628003</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.36186775671206</v>
       </c>
       <c r="E6">
-        <v>-8.851361900574091</v>
+        <v>-10.29301971481198</v>
       </c>
       <c r="F6">
-        <v>-4.296046865317595</v>
+        <v>-5.057035691940791</v>
       </c>
       <c r="G6">
-        <v>-12.33969209324222</v>
+        <v>-13.00445445629948</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.2890552784725</v>
       </c>
       <c r="E7">
-        <v>-8.978657304929705</v>
+        <v>-10.16919765002025</v>
       </c>
       <c r="F7">
-        <v>-4.291709533596537</v>
+        <v>-4.70567454600195</v>
       </c>
       <c r="G7">
-        <v>-12.64441257702473</v>
+        <v>-12.40818431207407</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.11457104426492</v>
       </c>
       <c r="E8">
-        <v>-9.644112031882855</v>
+        <v>-9.967173367590059</v>
       </c>
       <c r="F8">
-        <v>-4.077177286884715</v>
+        <v>-4.442076441287508</v>
       </c>
       <c r="G8">
-        <v>-12.53663429246165</v>
+        <v>-12.36375329093763</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.84032919289262</v>
       </c>
       <c r="E9">
-        <v>-10.08377704481356</v>
+        <v>-10.37931431550215</v>
       </c>
       <c r="F9">
-        <v>-3.599061846071702</v>
+        <v>-4.333261270888363</v>
       </c>
       <c r="G9">
-        <v>-12.8538923238228</v>
+        <v>-13.35174222737267</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.47756626650315</v>
       </c>
       <c r="E10">
-        <v>-10.77924196901555</v>
+        <v>-11.90403792846273</v>
       </c>
       <c r="F10">
-        <v>-3.926242119155423</v>
+        <v>-4.240356553194786</v>
       </c>
       <c r="G10">
-        <v>-13.02656988961014</v>
+        <v>-11.93148188147482</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.04605530605196</v>
       </c>
       <c r="E11">
-        <v>-12.07259225950223</v>
+        <v>-13.12106984649815</v>
       </c>
       <c r="F11">
-        <v>-3.621448475132358</v>
+        <v>-4.291282096016692</v>
       </c>
       <c r="G11">
-        <v>-12.28650021054206</v>
+        <v>-12.10606255576664</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.57517294045087</v>
       </c>
       <c r="E12">
-        <v>-12.23373347859117</v>
+        <v>-13.47324021312666</v>
       </c>
       <c r="F12">
-        <v>-3.635281382391707</v>
+        <v>-4.664218070961446</v>
       </c>
       <c r="G12">
-        <v>-12.86530113118499</v>
+        <v>-11.88795647748879</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.09566775690092</v>
       </c>
       <c r="E13">
-        <v>-12.62597178323955</v>
+        <v>-14.25187056247951</v>
       </c>
       <c r="F13">
-        <v>-3.560160056101431</v>
+        <v>-3.832502407119825</v>
       </c>
       <c r="G13">
-        <v>-12.51704539975176</v>
+        <v>-10.8877942090682</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.645719885486809</v>
       </c>
       <c r="E14">
-        <v>-12.94919161553702</v>
+        <v>-14.68310808528194</v>
       </c>
       <c r="F14">
-        <v>-3.52248590662211</v>
+        <v>-3.858995253396158</v>
       </c>
       <c r="G14">
-        <v>-11.50482792332178</v>
+        <v>-11.23335277637957</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.254481380875175</v>
       </c>
       <c r="E15">
-        <v>-13.42608974175879</v>
+        <v>-15.14781103100105</v>
       </c>
       <c r="F15">
-        <v>-2.896814208715824</v>
+        <v>-3.554456746533157</v>
       </c>
       <c r="G15">
-        <v>-10.67531870698636</v>
+        <v>-10.80860192673101</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.951901983459905</v>
       </c>
       <c r="E16">
-        <v>-13.17633534328776</v>
+        <v>-15.14788348658518</v>
       </c>
       <c r="F16">
-        <v>-3.394513911665823</v>
+        <v>-3.445687964708568</v>
       </c>
       <c r="G16">
-        <v>-11.00623974492104</v>
+        <v>-10.72035019166818</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.751936512015901</v>
       </c>
       <c r="E17">
-        <v>-15.13444750420442</v>
+        <v>-16.87224487617391</v>
       </c>
       <c r="F17">
-        <v>-2.850742898874324</v>
+        <v>-3.228442814752578</v>
       </c>
       <c r="G17">
-        <v>-10.07232205856409</v>
+        <v>-8.46344069132156</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.667578836585426</v>
       </c>
       <c r="E18">
-        <v>-15.03178246997653</v>
+        <v>-17.50620406640371</v>
       </c>
       <c r="F18">
-        <v>-2.565005846952662</v>
+        <v>-3.123843206066279</v>
       </c>
       <c r="G18">
-        <v>-9.778052265448407</v>
+        <v>-10.08545678846654</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.690766093242145</v>
       </c>
       <c r="E19">
-        <v>-16.46037563670228</v>
+        <v>-18.8549919356923</v>
       </c>
       <c r="F19">
-        <v>-2.387535586209493</v>
+        <v>-3.183784699700253</v>
       </c>
       <c r="G19">
-        <v>-9.53499577843254</v>
+        <v>-9.53321735634732</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.811878070480798</v>
       </c>
       <c r="E20">
-        <v>-16.64446263358809</v>
+        <v>-18.24720279675282</v>
       </c>
       <c r="F20">
-        <v>-1.878029162667393</v>
+        <v>-2.276291642585339</v>
       </c>
       <c r="G20">
-        <v>-8.555091771919969</v>
+        <v>-9.753311854890194</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.00058371700746</v>
       </c>
       <c r="E21">
-        <v>-18.03038398973958</v>
+        <v>-19.43225010287206</v>
       </c>
       <c r="F21">
-        <v>-1.48135383469321</v>
+        <v>-2.329416500861677</v>
       </c>
       <c r="G21">
-        <v>-8.01085852040579</v>
+        <v>-9.803196266258432</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.229493083839888</v>
       </c>
       <c r="E22">
-        <v>-16.85241921696833</v>
+        <v>-19.43967227177064</v>
       </c>
       <c r="F22">
-        <v>-1.44158805752182</v>
+        <v>-1.687372121239059</v>
       </c>
       <c r="G22">
-        <v>-8.478905088531222</v>
+        <v>-9.048781086532461</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.45951817121532</v>
       </c>
       <c r="E23">
-        <v>-18.73343863637841</v>
+        <v>-21.01227091194031</v>
       </c>
       <c r="F23">
-        <v>-1.101283131308144</v>
+        <v>-1.539682496993935</v>
       </c>
       <c r="G23">
-        <v>-8.246040075678991</v>
+        <v>-8.214717534672531</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.66162381938951</v>
       </c>
       <c r="E24">
-        <v>-19.57564423232495</v>
+        <v>-21.46370995729096</v>
       </c>
       <c r="F24">
-        <v>-1.225832312156064</v>
+        <v>-1.581180390404579</v>
       </c>
       <c r="G24">
-        <v>-8.234926578257152</v>
+        <v>-9.207434711374733</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.803202977861851</v>
       </c>
       <c r="E25">
-        <v>-18.80651462144019</v>
+        <v>-21.28255288308812</v>
       </c>
       <c r="F25">
-        <v>-1.048650323269069</v>
+        <v>-1.418484890657742</v>
       </c>
       <c r="G25">
-        <v>-8.099799311996099</v>
+        <v>-9.14269292878533</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.865050657051437</v>
       </c>
       <c r="E26">
-        <v>-20.51894801049272</v>
+        <v>-21.90029560789646</v>
       </c>
       <c r="F26">
-        <v>-1.138324408091727</v>
+        <v>-1.070029657567922</v>
       </c>
       <c r="G26">
-        <v>-8.174118980317521</v>
+        <v>-8.477376039284522</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.830251136938589</v>
       </c>
       <c r="E27">
-        <v>-20.22334281269402</v>
+        <v>-23.15602333632742</v>
       </c>
       <c r="F27">
-        <v>-1.095636979090663</v>
+        <v>-1.478096694065403</v>
       </c>
       <c r="G27">
-        <v>-8.450509397155788</v>
+        <v>-8.608785681518723</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.695047996593564</v>
       </c>
       <c r="E28">
-        <v>-19.80171471173587</v>
+        <v>-23.14489234721656</v>
       </c>
       <c r="F28">
-        <v>-1.148236652433626</v>
+        <v>-1.197301682068843</v>
       </c>
       <c r="G28">
-        <v>-7.997077389856122</v>
+        <v>-10.33135481335289</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.461544496456693</v>
       </c>
       <c r="E29">
-        <v>-19.21278213856433</v>
+        <v>-20.92287430655489</v>
       </c>
       <c r="F29">
-        <v>-1.387870916552481</v>
+        <v>-1.379115901472293</v>
       </c>
       <c r="G29">
-        <v>-8.671450450860998</v>
+        <v>-9.068875287362502</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.141721613074184</v>
       </c>
       <c r="E30">
-        <v>-20.19573723514326</v>
+        <v>-20.75337352444779</v>
       </c>
       <c r="F30">
-        <v>-1.350615920978976</v>
+        <v>-1.342386090832163</v>
       </c>
       <c r="G30">
-        <v>-7.986734979500753</v>
+        <v>-9.355640926771732</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.753915605881394</v>
       </c>
       <c r="E31">
-        <v>-18.9320982626209</v>
+        <v>-21.16265700526104</v>
       </c>
       <c r="F31">
-        <v>-1.421008097766669</v>
+        <v>-1.672526120646086</v>
       </c>
       <c r="G31">
-        <v>-8.542301570281253</v>
+        <v>-7.973035879490071</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.318128037293826</v>
       </c>
       <c r="E32">
-        <v>-20.14662593453008</v>
+        <v>-20.40752037905999</v>
       </c>
       <c r="F32">
-        <v>-1.704545834233898</v>
+        <v>-1.659156270764902</v>
       </c>
       <c r="G32">
-        <v>-7.936325572683004</v>
+        <v>-8.286773160117937</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.859779554836336</v>
       </c>
       <c r="E33">
-        <v>-19.33547208485414</v>
+        <v>-20.89251541680747</v>
       </c>
       <c r="F33">
-        <v>-1.565153966262617</v>
+        <v>-1.444781413859612</v>
       </c>
       <c r="G33">
-        <v>-7.993264610404048</v>
+        <v>-8.691465902373611</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.399341969088768</v>
       </c>
       <c r="E34">
-        <v>-19.90399935414712</v>
+        <v>-21.3718091057793</v>
       </c>
       <c r="F34">
-        <v>-1.739221293715085</v>
+        <v>-1.538364564456081</v>
       </c>
       <c r="G34">
-        <v>-7.693403615751074</v>
+        <v>-8.424919150213679</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.963146256861834</v>
       </c>
       <c r="E35">
-        <v>-19.87578696107933</v>
+        <v>-21.23888027975815</v>
       </c>
       <c r="F35">
-        <v>-1.562366509952196</v>
+        <v>-1.92230043014261</v>
       </c>
       <c r="G35">
-        <v>-6.967971466059679</v>
+        <v>-8.324891110974006</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.566695836812208</v>
       </c>
       <c r="E36">
-        <v>-18.66834182251815</v>
+        <v>-19.55844055956981</v>
       </c>
       <c r="F36">
-        <v>-1.589940375689184</v>
+        <v>-1.482390950681515</v>
       </c>
       <c r="G36">
-        <v>-7.480232494698629</v>
+        <v>-7.732820930344683</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.229513271161646</v>
       </c>
       <c r="E37">
-        <v>-18.6355466137546</v>
+        <v>-21.0332196326998</v>
       </c>
       <c r="F37">
-        <v>-1.773697945019601</v>
+        <v>-1.593279524689869</v>
       </c>
       <c r="G37">
-        <v>-6.63079313861114</v>
+        <v>-7.638781120450997</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.957493527213479</v>
       </c>
       <c r="E38">
-        <v>-19.35156175300339</v>
+        <v>-20.21629650713809</v>
       </c>
       <c r="F38">
-        <v>-1.805887473924987</v>
+        <v>-1.599787179006261</v>
       </c>
       <c r="G38">
-        <v>-6.882649861849439</v>
+        <v>-7.549882984740962</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.760362119750555</v>
       </c>
       <c r="E39">
-        <v>-18.13604687376055</v>
+        <v>-20.15130837665401</v>
       </c>
       <c r="F39">
-        <v>-1.808824864735314</v>
+        <v>-1.857860901511433</v>
       </c>
       <c r="G39">
-        <v>-6.403959010985168</v>
+        <v>-6.091212659268254</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.633631169416915</v>
       </c>
       <c r="E40">
-        <v>-19.4337490277686</v>
+        <v>-19.414498484762</v>
       </c>
       <c r="F40">
-        <v>-1.536333407584416</v>
+        <v>-1.439683640862784</v>
       </c>
       <c r="G40">
-        <v>-6.873288536740342</v>
+        <v>-6.509591376648372</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.575957349900863</v>
       </c>
       <c r="E41">
-        <v>-16.95110825101749</v>
+        <v>-18.47754362715298</v>
       </c>
       <c r="F41">
-        <v>-1.691369822324969</v>
+        <v>-1.8578509611026</v>
       </c>
       <c r="G41">
-        <v>-6.965884609147873</v>
+        <v>-6.644718642909424</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.573767212194034</v>
       </c>
       <c r="E42">
-        <v>-18.08651442506465</v>
+        <v>-20.29912229673838</v>
       </c>
       <c r="F42">
-        <v>-1.560401622472756</v>
+        <v>-1.965061583842523</v>
       </c>
       <c r="G42">
-        <v>-6.268513466232849</v>
+        <v>-6.176110985897327</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.617840426055136</v>
       </c>
       <c r="E43">
-        <v>-18.53953390784397</v>
+        <v>-18.69409525419977</v>
       </c>
       <c r="F43">
-        <v>-1.454017710400827</v>
+        <v>-1.866645737818122</v>
       </c>
       <c r="G43">
-        <v>-5.61171462790036</v>
+        <v>-6.158284109164864</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.690436552138508</v>
       </c>
       <c r="E44">
-        <v>-17.9782703108593</v>
+        <v>-18.68665497140517</v>
       </c>
       <c r="F44">
-        <v>-1.544430698946782</v>
+        <v>-2.001787252645639</v>
       </c>
       <c r="G44">
-        <v>-6.12172801977109</v>
+        <v>-6.696256789943622</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.779885252106693</v>
       </c>
       <c r="E45">
-        <v>-17.49852830296071</v>
+        <v>-18.83549685508928</v>
       </c>
       <c r="F45">
-        <v>-1.918161906598223</v>
+        <v>-2.02583807181852</v>
       </c>
       <c r="G45">
-        <v>-5.038855999501585</v>
+        <v>-6.737560806933912</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.870250369709503</v>
       </c>
       <c r="E46">
-        <v>-17.53207976688354</v>
+        <v>-18.48684058429073</v>
       </c>
       <c r="F46">
-        <v>-1.872971151305899</v>
+        <v>-1.771372717719943</v>
       </c>
       <c r="G46">
-        <v>-5.134090174042909</v>
+        <v>-5.718249329492411</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.953717912425557</v>
       </c>
       <c r="E47">
-        <v>-16.8616120192039</v>
+        <v>-17.28693535495232</v>
       </c>
       <c r="F47">
-        <v>-1.785552710921064</v>
+        <v>-2.458469515278618</v>
       </c>
       <c r="G47">
-        <v>-5.525041160407627</v>
+        <v>-6.903961395878031</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.021257144479764</v>
       </c>
       <c r="E48">
-        <v>-16.76935794671964</v>
+        <v>-17.85961070643632</v>
       </c>
       <c r="F48">
-        <v>-1.990535538213413</v>
+        <v>-1.963656672727375</v>
       </c>
       <c r="G48">
-        <v>-4.84678313307637</v>
+        <v>-5.151674240379973</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.072112987955888</v>
       </c>
       <c r="E49">
-        <v>-16.14548819657893</v>
+        <v>-17.63506632276598</v>
       </c>
       <c r="F49">
-        <v>-2.029380999200293</v>
+        <v>-2.244161756132955</v>
       </c>
       <c r="G49">
-        <v>-5.155204834777935</v>
+        <v>-5.555937142611359</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.104951208822733</v>
       </c>
       <c r="E50">
-        <v>-16.38472747840415</v>
+        <v>-17.76414141740661</v>
       </c>
       <c r="F50">
-        <v>-1.952908605676051</v>
+        <v>-2.139839650526593</v>
       </c>
       <c r="G50">
-        <v>-4.531546334195838</v>
+        <v>-5.327915212780868</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.125381517944963</v>
       </c>
       <c r="E51">
-        <v>-16.19000762454833</v>
+        <v>-17.00283700960711</v>
       </c>
       <c r="F51">
-        <v>-2.21765979781519</v>
+        <v>-2.069131865758433</v>
       </c>
       <c r="G51">
-        <v>-4.398614205158054</v>
+        <v>-5.884603981334699</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.137701142957808</v>
       </c>
       <c r="E52">
-        <v>-16.08819847190789</v>
+        <v>-16.63499359443805</v>
       </c>
       <c r="F52">
-        <v>-2.202206603915966</v>
+        <v>-2.769178530925073</v>
       </c>
       <c r="G52">
-        <v>-4.901776406412663</v>
+        <v>-4.937978123878017</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.149793911587588</v>
       </c>
       <c r="E53">
-        <v>-14.90909252368671</v>
+        <v>-16.64241576333663</v>
       </c>
       <c r="F53">
-        <v>-2.597524237716959</v>
+        <v>-2.112472876640306</v>
       </c>
       <c r="G53">
-        <v>-4.411584873982539</v>
+        <v>-5.540167591796668</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.166839807767416</v>
       </c>
       <c r="E54">
-        <v>-15.37701521442528</v>
+        <v>-16.01004606748351</v>
       </c>
       <c r="F54">
-        <v>-2.484818225626864</v>
+        <v>-2.978246037880626</v>
       </c>
       <c r="G54">
-        <v>-4.263368814920862</v>
+        <v>-5.380490225827851</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.194323172737245</v>
       </c>
       <c r="E55">
-        <v>-15.57308908200939</v>
+        <v>-15.67385215715407</v>
       </c>
       <c r="F55">
-        <v>-2.121855794211816</v>
+        <v>-2.486980264548171</v>
       </c>
       <c r="G55">
-        <v>-4.717722845478731</v>
+        <v>-5.135510942978148</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.235492998732563</v>
       </c>
       <c r="E56">
-        <v>-15.16085303614314</v>
+        <v>-15.13590567283489</v>
       </c>
       <c r="F56">
-        <v>-2.471259507977842</v>
+        <v>-2.01255520051463</v>
       </c>
       <c r="G56">
-        <v>-4.389495690444357</v>
+        <v>-6.366415273902001</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.291198088849685</v>
       </c>
       <c r="E57">
-        <v>-14.22930517649928</v>
+        <v>-15.47297810712183</v>
       </c>
       <c r="F57">
-        <v>-2.282982366097751</v>
+        <v>-2.89246942168814</v>
       </c>
       <c r="G57">
-        <v>-4.439642599537351</v>
+        <v>-5.743157082350156</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.36256188229263</v>
       </c>
       <c r="E58">
-        <v>-13.84167685839072</v>
+        <v>-15.06402067643713</v>
       </c>
       <c r="F58">
-        <v>-2.544156667791601</v>
+        <v>-2.858221399786797</v>
       </c>
       <c r="G58">
-        <v>-5.051662607248098</v>
+        <v>-6.268556122113122</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.446495102729887</v>
       </c>
       <c r="E59">
-        <v>-14.11509706202584</v>
+        <v>-15.02273910738321</v>
       </c>
       <c r="F59">
-        <v>-2.493601405198747</v>
+        <v>-2.566781866664264</v>
       </c>
       <c r="G59">
-        <v>-5.008950946208806</v>
+        <v>-5.969886210886227</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.542374000619421</v>
       </c>
       <c r="E60">
-        <v>-13.90246256499568</v>
+        <v>-14.19893270132984</v>
       </c>
       <c r="F60">
-        <v>-2.382846198342245</v>
+        <v>-2.830331097701941</v>
       </c>
       <c r="G60">
-        <v>-5.573993704852984</v>
+        <v>-5.886205217455708</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.644133690905617</v>
       </c>
       <c r="E61">
-        <v>-14.11239809151727</v>
+        <v>-13.45256320080763</v>
       </c>
       <c r="F61">
-        <v>-2.163140797199941</v>
+        <v>-2.828717438001287</v>
       </c>
       <c r="G61">
-        <v>-5.809276977994526</v>
+        <v>-7.246537332791857</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.750760262997049</v>
       </c>
       <c r="E62">
-        <v>-14.01932889371163</v>
+        <v>-14.40241968086451</v>
       </c>
       <c r="F62">
-        <v>-2.408682977635562</v>
+        <v>-2.408819658257024</v>
       </c>
       <c r="G62">
-        <v>-5.462484671376814</v>
+        <v>-7.103147950644123</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.855792243209624</v>
       </c>
       <c r="E63">
-        <v>-13.38166541174355</v>
+        <v>-13.19191329387414</v>
       </c>
       <c r="F63">
-        <v>-2.65017361310409</v>
+        <v>-2.547296180248212</v>
       </c>
       <c r="G63">
-        <v>-6.108832819042473</v>
+        <v>-6.390761937873081</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.960005668435054</v>
       </c>
       <c r="E64">
-        <v>-13.39863360385029</v>
+        <v>-13.77472789866132</v>
       </c>
       <c r="F64">
-        <v>-2.601586551460288</v>
+        <v>-2.177428478163427</v>
       </c>
       <c r="G64">
-        <v>-5.59139074156116</v>
+        <v>-7.151627999184919</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.058580753048037</v>
       </c>
       <c r="E65">
-        <v>-13.32057629738007</v>
+        <v>-13.7015070024313</v>
       </c>
       <c r="F65">
-        <v>-2.305756671102918</v>
+        <v>-2.292960051464471</v>
       </c>
       <c r="G65">
-        <v>-5.935892755530379</v>
+        <v>-7.863367611308751</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.155624776624103</v>
       </c>
       <c r="E66">
-        <v>-13.35523723743478</v>
+        <v>-13.1271832864085</v>
       </c>
       <c r="F66">
-        <v>-2.491967864680427</v>
+        <v>-2.911458087662513</v>
       </c>
       <c r="G66">
-        <v>-6.79063456565793</v>
+        <v>-6.967154441891378</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.249716920907601</v>
       </c>
       <c r="E67">
-        <v>-13.35089443086143</v>
+        <v>-14.11344869748705</v>
       </c>
       <c r="F67">
-        <v>-2.470540485072212</v>
+        <v>-2.389509585730365</v>
       </c>
       <c r="G67">
-        <v>-6.511658546230821</v>
+        <v>-7.601985501883385</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.3478316796059</v>
       </c>
       <c r="E68">
-        <v>-12.86927763472366</v>
+        <v>-12.85479104637312</v>
       </c>
       <c r="F68">
-        <v>-2.629926657044865</v>
+        <v>-2.562860375379411</v>
       </c>
       <c r="G68">
-        <v>-6.181662812775907</v>
+        <v>-8.122242867462701</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.449809510158713</v>
       </c>
       <c r="E69">
-        <v>-13.67105754320372</v>
+        <v>-12.9522483354922</v>
       </c>
       <c r="F69">
-        <v>-2.36674190766442</v>
+        <v>-2.643899558395287</v>
       </c>
       <c r="G69">
-        <v>-6.527054037787736</v>
+        <v>-8.056270626788505</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.562470836739449</v>
       </c>
       <c r="E70">
-        <v>-13.32013250692732</v>
+        <v>-12.62109914520729</v>
       </c>
       <c r="F70">
-        <v>-2.605228054562995</v>
+        <v>-2.502547773148982</v>
       </c>
       <c r="G70">
-        <v>-6.363718109780137</v>
+        <v>-8.58026202250247</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.684382742410622</v>
       </c>
       <c r="E71">
-        <v>-14.20409969017259</v>
+        <v>-13.1901154896931</v>
       </c>
       <c r="F71">
-        <v>-2.265176608774575</v>
+        <v>-3.141670500941927</v>
       </c>
       <c r="G71">
-        <v>-7.054786026079467</v>
+        <v>-7.642242809196212</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.819733876669504</v>
       </c>
       <c r="E72">
-        <v>-13.87335806254838</v>
+        <v>-13.54632978361046</v>
       </c>
       <c r="F72">
-        <v>-2.849961748413484</v>
+        <v>-2.967005092224637</v>
       </c>
       <c r="G72">
-        <v>-6.559774379178519</v>
+        <v>-8.296433076388942</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.965482756720965</v>
       </c>
       <c r="E73">
-        <v>-13.68974202695937</v>
+        <v>-13.69510826865846</v>
       </c>
       <c r="F73">
-        <v>-2.995675716402931</v>
+        <v>-3.046983964964929</v>
       </c>
       <c r="G73">
-        <v>-6.602013544313251</v>
+        <v>-8.285719887997356</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.123081149378738</v>
       </c>
       <c r="E74">
-        <v>-14.39761949841638</v>
+        <v>-13.36267299175538</v>
       </c>
       <c r="F74">
-        <v>-2.910139326757256</v>
+        <v>-2.917757821760804</v>
       </c>
       <c r="G74">
-        <v>-6.254236871227706</v>
+        <v>-7.988008093465818</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.289695623786871</v>
       </c>
       <c r="E75">
-        <v>-14.39688588562713</v>
+        <v>-13.22293334082669</v>
       </c>
       <c r="F75">
-        <v>-2.901743823129884</v>
+        <v>-2.913325227788424</v>
       </c>
       <c r="G75">
-        <v>-5.953371822777541</v>
+        <v>-7.498387493587036</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.464595990771159</v>
       </c>
       <c r="E76">
-        <v>-13.68998203608177</v>
+        <v>-13.61024013728071</v>
       </c>
       <c r="F76">
-        <v>-3.151316839347527</v>
+        <v>-3.611000277080848</v>
       </c>
       <c r="G76">
-        <v>-6.146911395239828</v>
+        <v>-8.153988686050328</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.645383953724336</v>
       </c>
       <c r="E77">
-        <v>-14.9693665127288</v>
+        <v>-14.70320092445397</v>
       </c>
       <c r="F77">
-        <v>-3.045947677344027</v>
+        <v>-3.244295281739952</v>
       </c>
       <c r="G77">
-        <v>-5.863594319689574</v>
+        <v>-8.377968150919584</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.828105875615028</v>
       </c>
       <c r="E78">
-        <v>-14.52621457481219</v>
+        <v>-14.66725842625509</v>
       </c>
       <c r="F78">
-        <v>-2.960719440372194</v>
+        <v>-2.993103635617238</v>
       </c>
       <c r="G78">
-        <v>-6.160157686675307</v>
+        <v>-6.896227556662421</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.010335289144559</v>
       </c>
       <c r="E79">
-        <v>-14.84524104017856</v>
+        <v>-15.20497395839988</v>
       </c>
       <c r="F79">
-        <v>-3.319022305146495</v>
+        <v>-3.522922456243385</v>
       </c>
       <c r="G79">
-        <v>-6.008539000856485</v>
+        <v>-6.831577648276681</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.185118444302832</v>
       </c>
       <c r="E80">
-        <v>-15.73160378617389</v>
+        <v>-14.73336056134506</v>
       </c>
       <c r="F80">
-        <v>-3.136129551384601</v>
+        <v>-3.260542051611059</v>
       </c>
       <c r="G80">
-        <v>-5.698676842890324</v>
+        <v>-7.064209694398193</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.35073826697452</v>
       </c>
       <c r="E81">
-        <v>-15.61601901560211</v>
+        <v>-16.34298853347545</v>
       </c>
       <c r="F81">
-        <v>-3.190457199129804</v>
+        <v>-3.802374684680007</v>
       </c>
       <c r="G81">
-        <v>-5.088428694821676</v>
+        <v>-7.163489615122312</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.499758972536297</v>
       </c>
       <c r="E82">
-        <v>-16.17351945068641</v>
+        <v>-17.20295480448007</v>
       </c>
       <c r="F82">
-        <v>-3.347082422548926</v>
+        <v>-3.625204292936651</v>
       </c>
       <c r="G82">
-        <v>-5.807974333035427</v>
+        <v>-6.05560484290516</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.632714993841464</v>
       </c>
       <c r="E83">
-        <v>-17.47952682602453</v>
+        <v>-17.81310780685155</v>
       </c>
       <c r="F83">
-        <v>-3.795073454391732</v>
+        <v>-3.797939605605418</v>
       </c>
       <c r="G83">
-        <v>-5.797520361147036</v>
+        <v>-7.235610864998907</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.743208464423905</v>
       </c>
       <c r="E84">
-        <v>-18.14628575349189</v>
+        <v>-18.36038747610054</v>
       </c>
       <c r="F84">
-        <v>-3.885423487015074</v>
+        <v>-3.774100848487654</v>
       </c>
       <c r="G84">
-        <v>-5.434456476816037</v>
+        <v>-6.648268924636743</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.835247333938067</v>
       </c>
       <c r="E85">
-        <v>-19.31306066699018</v>
+        <v>-19.32103078124368</v>
       </c>
       <c r="F85">
-        <v>-4.089355944440674</v>
+        <v>-4.100223296398</v>
       </c>
       <c r="G85">
-        <v>-5.195718077372399</v>
+        <v>-6.244124146381496</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.90587931033482</v>
       </c>
       <c r="E86">
-        <v>-19.84912330612217</v>
+        <v>-19.32286481321679</v>
       </c>
       <c r="F86">
-        <v>-4.089952368970689</v>
+        <v>-4.311766793520521</v>
       </c>
       <c r="G86">
-        <v>-5.533710147767681</v>
+        <v>-5.793973360641276</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.963654781230046</v>
       </c>
       <c r="E87">
-        <v>-20.56253004434254</v>
+        <v>-20.92694540468779</v>
       </c>
       <c r="F87">
-        <v>-4.35971684063157</v>
+        <v>-4.128900547515516</v>
       </c>
       <c r="G87">
-        <v>-5.143228376085962</v>
+        <v>-6.899830337934691</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.00939724026163</v>
       </c>
       <c r="E88">
-        <v>-21.47874449099643</v>
+        <v>-21.6770961810064</v>
       </c>
       <c r="F88">
-        <v>-4.635438930653385</v>
+        <v>-4.362281466110637</v>
       </c>
       <c r="G88">
-        <v>-5.90285741686989</v>
+        <v>-6.464153020493181</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.05469499708187</v>
       </c>
       <c r="E89">
-        <v>-23.61862507010697</v>
+        <v>-22.22158178179265</v>
       </c>
       <c r="F89">
-        <v>-4.674080613259177</v>
+        <v>-4.920332704558997</v>
       </c>
       <c r="G89">
-        <v>-5.528073009128555</v>
+        <v>-6.184848878910128</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.10326965844769</v>
       </c>
       <c r="E90">
-        <v>-24.71709248167356</v>
+        <v>-25.5149054469229</v>
       </c>
       <c r="F90">
-        <v>-4.494884863215977</v>
+        <v>-4.727298248684629</v>
       </c>
       <c r="G90">
-        <v>-5.629895876561243</v>
+        <v>-6.922165613089831</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.16729907750714</v>
       </c>
       <c r="E91">
-        <v>-26.21779706849746</v>
+        <v>-26.08724569133034</v>
       </c>
       <c r="F91">
-        <v>-4.760938248912316</v>
+        <v>-5.029200062104519</v>
       </c>
       <c r="G91">
-        <v>-5.545778480663318</v>
+        <v>-6.208896951719298</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.25032356430742</v>
       </c>
       <c r="E92">
-        <v>-27.52097414758079</v>
+        <v>-28.8275022974298</v>
       </c>
       <c r="F92">
-        <v>-5.074278159430063</v>
+        <v>-4.341994748416077</v>
       </c>
       <c r="G92">
-        <v>-5.622102975357562</v>
+        <v>-6.182253432656607</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.36044275735586</v>
       </c>
       <c r="E93">
-        <v>-30.18740530617021</v>
+        <v>-30.60970814975551</v>
       </c>
       <c r="F93">
-        <v>-4.98086813762078</v>
+        <v>-4.546614750786</v>
       </c>
       <c r="G93">
-        <v>-6.13626383127943</v>
+        <v>-6.245863193808002</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.4972561580518</v>
       </c>
       <c r="E94">
-        <v>-31.62133301527701</v>
+        <v>-31.15340126759043</v>
       </c>
       <c r="F94">
-        <v>-4.990936943401808</v>
+        <v>-4.769148198241462</v>
       </c>
       <c r="G94">
-        <v>-6.092344680706263</v>
+        <v>-7.031892943259222</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.66099453125292</v>
       </c>
       <c r="E95">
-        <v>-33.1499556443582</v>
+        <v>-35.57720639128449</v>
       </c>
       <c r="F95">
-        <v>-5.147999544809608</v>
+        <v>-4.854119641318428</v>
       </c>
       <c r="G95">
-        <v>-6.708252935964952</v>
+        <v>-7.918751350010618</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.84605738483722</v>
       </c>
       <c r="E96">
-        <v>-36.63353635220971</v>
+        <v>-35.80981145868848</v>
       </c>
       <c r="F96">
-        <v>-5.212719061622931</v>
+        <v>-4.877818404345118</v>
       </c>
       <c r="G96">
-        <v>-7.121732789556818</v>
+        <v>-7.5504867295079</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.04230545409338</v>
       </c>
       <c r="E97">
-        <v>-37.98915995301287</v>
+        <v>-38.75073606925284</v>
       </c>
       <c r="F97">
-        <v>-5.468926472369595</v>
+        <v>-5.051000207043994</v>
       </c>
       <c r="G97">
-        <v>-6.794604843744859</v>
+        <v>-7.947701567829599</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.24004051368447</v>
       </c>
       <c r="E98">
-        <v>-40.08543359166656</v>
+        <v>-41.36278478348414</v>
       </c>
       <c r="F98">
-        <v>-5.151877960989515</v>
+        <v>-4.928081253244784</v>
       </c>
       <c r="G98">
-        <v>-7.290650075437032</v>
+        <v>-8.194495366201673</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.42303068541643</v>
       </c>
       <c r="E99">
-        <v>-42.36872641412601</v>
+        <v>-43.30780512604463</v>
       </c>
       <c r="F99">
-        <v>-5.021315661164674</v>
+        <v>-5.300674284084779</v>
       </c>
       <c r="G99">
-        <v>-7.528397545969717</v>
+        <v>-8.308202818122671</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.58379015677976</v>
       </c>
       <c r="E100">
-        <v>-44.89898862354178</v>
+        <v>-45.62900354018529</v>
       </c>
       <c r="F100">
-        <v>-4.892275072258776</v>
+        <v>-4.906089755435262</v>
       </c>
       <c r="G100">
-        <v>-8.063545094985795</v>
+        <v>-8.588153360352935</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.70545191472825</v>
       </c>
       <c r="E101">
-        <v>-47.06037266147775</v>
+        <v>-47.57099659787165</v>
       </c>
       <c r="F101">
-        <v>-4.682787583030002</v>
+        <v>-4.407713276317176</v>
       </c>
       <c r="G101">
-        <v>-8.974773134259186</v>
+        <v>-9.403618948413932</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.78577020304106</v>
       </c>
       <c r="E102">
-        <v>-49.93500607316232</v>
+        <v>-50.59178537603528</v>
       </c>
       <c r="F102">
-        <v>-4.421694461341627</v>
+        <v>-4.456948121269968</v>
       </c>
       <c r="G102">
-        <v>-8.664307231526086</v>
+        <v>-9.582281462325698</v>
       </c>
     </row>
   </sheetData>
